--- a/AAII_Financials/Yearly/DNBBY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DNBBY_YR_FIN.xlsx
@@ -2141,10 +2141,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>150969000</v>
+        <v>151170900</v>
       </c>
       <c r="E57" s="3">
-        <v>130955100</v>
+        <v>131047000</v>
       </c>
       <c r="F57" s="3">
         <v>140424600</v>
@@ -2174,10 +2174,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>57268700</v>
+        <v>57314300</v>
       </c>
       <c r="E58" s="3">
-        <v>49967000</v>
+        <v>50008000</v>
       </c>
       <c r="F58" s="3">
         <v>60357900</v>
@@ -2207,10 +2207,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1356400</v>
+        <v>1579300</v>
       </c>
       <c r="E59" s="3">
-        <v>322400</v>
+        <v>584600</v>
       </c>
       <c r="F59" s="3">
         <v>1314000</v>
@@ -2240,10 +2240,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>209594100</v>
+        <v>210833800</v>
       </c>
       <c r="E60" s="3">
-        <v>181244600</v>
+        <v>182186500</v>
       </c>
       <c r="F60" s="3">
         <v>202584500</v>
@@ -2273,10 +2273,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>78469600</v>
+        <v>78676600</v>
       </c>
       <c r="E61" s="3">
-        <v>70150600</v>
+        <v>70301000</v>
       </c>
       <c r="F61" s="3">
         <v>72358700</v>
@@ -2306,10 +2306,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>48257700</v>
+        <v>46811100</v>
       </c>
       <c r="E62" s="3">
-        <v>40870000</v>
+        <v>39777600</v>
       </c>
       <c r="F62" s="3">
         <v>36917300</v>
